--- a/artfynd/A 7951-2026 artfynd.xlsx
+++ b/artfynd/A 7951-2026 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131699481</v>
+        <v>131704892</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>79879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,39 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454462</v>
+        <v>454246</v>
       </c>
       <c r="R4" t="n">
-        <v>6762674</v>
+        <v>6762660</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131698769</v>
+        <v>131699481</v>
       </c>
       <c r="B5" t="n">
         <v>57898</v>
@@ -1002,7 +997,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454359</v>
+        <v>454462</v>
       </c>
       <c r="R5" t="n">
-        <v>6762685</v>
+        <v>6762674</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131704892</v>
+        <v>131698769</v>
       </c>
       <c r="B6" t="n">
-        <v>79879</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,34 +1079,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454246</v>
+        <v>454359</v>
       </c>
       <c r="R6" t="n">
-        <v>6762660</v>
+        <v>6762685</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1471,53 +1471,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131704688</v>
+        <v>131702441</v>
       </c>
       <c r="B10" t="n">
-        <v>57086</v>
+        <v>79260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454233</v>
+        <v>454300</v>
       </c>
       <c r="R10" t="n">
-        <v>6762667</v>
+        <v>6762775</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1551,7 +1546,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Under tjädertall</t>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,48 +1573,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131702441</v>
+        <v>131704688</v>
       </c>
       <c r="B11" t="n">
-        <v>79260</v>
+        <v>57086</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454300</v>
+        <v>454233</v>
       </c>
       <c r="R11" t="n">
-        <v>6762775</v>
+        <v>6762667</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
+          <t>Under tjädertall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,45 +1680,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131698785</v>
+        <v>131701172</v>
       </c>
       <c r="B12" t="n">
-        <v>79260</v>
+        <v>8453</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454359</v>
+        <v>454329</v>
       </c>
       <c r="R12" t="n">
-        <v>6762685</v>
+        <v>6762746</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1879,50 +1884,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131701172</v>
+        <v>131698785</v>
       </c>
       <c r="B14" t="n">
-        <v>8453</v>
+        <v>79260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454329</v>
+        <v>454359</v>
       </c>
       <c r="R14" t="n">
-        <v>6762746</v>
+        <v>6762685</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2078,10 +2078,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131701058</v>
+        <v>131699011</v>
       </c>
       <c r="B16" t="n">
-        <v>79850</v>
+        <v>57895</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2089,34 +2089,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454329</v>
+        <v>454431</v>
       </c>
       <c r="R16" t="n">
-        <v>6762746</v>
+        <v>6762675</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2175,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131699011</v>
+        <v>131701058</v>
       </c>
       <c r="B17" t="n">
-        <v>57895</v>
+        <v>79850</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2186,39 +2191,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454431</v>
+        <v>454329</v>
       </c>
       <c r="R17" t="n">
-        <v>6762675</v>
+        <v>6762746</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2277,50 +2277,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131700699</v>
+        <v>131700625</v>
       </c>
       <c r="B18" t="n">
-        <v>8453</v>
+        <v>79260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454367</v>
+        <v>454380</v>
       </c>
       <c r="R18" t="n">
-        <v>6762713</v>
+        <v>6762722</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2379,45 +2374,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131700625</v>
+        <v>131700699</v>
       </c>
       <c r="B19" t="n">
-        <v>79260</v>
+        <v>8453</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454380</v>
+        <v>454367</v>
       </c>
       <c r="R19" t="n">
-        <v>6762722</v>
+        <v>6762713</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2476,7 +2476,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131699864</v>
+        <v>131704301</v>
       </c>
       <c r="B20" t="n">
         <v>79260</v>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454488</v>
+        <v>454291</v>
       </c>
       <c r="R20" t="n">
-        <v>6762699</v>
+        <v>6762688</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,11 +2547,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Miljöbilder och garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2578,7 +2573,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131704301</v>
+        <v>131699864</v>
       </c>
       <c r="B21" t="n">
         <v>79260</v>
@@ -2613,10 +2608,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454291</v>
+        <v>454488</v>
       </c>
       <c r="R21" t="n">
-        <v>6762688</v>
+        <v>6762699</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2649,6 +2644,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Miljöbilder och garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131699226</v>
+        <v>131701072</v>
       </c>
       <c r="B22" t="n">
-        <v>57898</v>
+        <v>79260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,39 +2686,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454445</v>
+        <v>454329</v>
       </c>
       <c r="R22" t="n">
-        <v>6762675</v>
+        <v>6762746</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2777,10 +2772,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131701072</v>
+        <v>131699226</v>
       </c>
       <c r="B23" t="n">
-        <v>79260</v>
+        <v>57898</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2788,34 +2783,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454329</v>
+        <v>454445</v>
       </c>
       <c r="R23" t="n">
-        <v>6762746</v>
+        <v>6762675</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3165,7 +3165,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131700143</v>
+        <v>131699230</v>
       </c>
       <c r="B27" t="n">
         <v>79260</v>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454452</v>
+        <v>454445</v>
       </c>
       <c r="R27" t="n">
-        <v>6762716</v>
+        <v>6762675</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3236,11 +3236,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt med garnlav i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3267,7 +3262,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131699230</v>
+        <v>131700143</v>
       </c>
       <c r="B28" t="n">
         <v>79260</v>
@@ -3302,13 +3297,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454445</v>
+        <v>454452</v>
       </c>
       <c r="R28" t="n">
-        <v>6762675</v>
+        <v>6762716</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3338,6 +3333,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt med garnlav i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3364,10 +3364,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131701164</v>
+        <v>131704877</v>
       </c>
       <c r="B29" t="n">
-        <v>57895</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3375,39 +3375,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454329</v>
+        <v>454246</v>
       </c>
       <c r="R29" t="n">
-        <v>6762746</v>
+        <v>6762660</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3563,10 +3558,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131704877</v>
+        <v>131701164</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>57895</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3574,34 +3569,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454246</v>
+        <v>454329</v>
       </c>
       <c r="R31" t="n">
-        <v>6762660</v>
+        <v>6762746</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3660,10 +3660,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131700614</v>
+        <v>131704895</v>
       </c>
       <c r="B32" t="n">
-        <v>79850</v>
+        <v>79260</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3671,21 +3671,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454380</v>
+        <v>454246</v>
       </c>
       <c r="R32" t="n">
-        <v>6762722</v>
+        <v>6762660</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3757,50 +3757,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131699709</v>
+        <v>131700019</v>
       </c>
       <c r="B33" t="n">
-        <v>8453</v>
+        <v>79260</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454510</v>
+        <v>454460</v>
       </c>
       <c r="R33" t="n">
-        <v>6762678</v>
+        <v>6762684</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3859,7 +3854,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131704895</v>
+        <v>131704692</v>
       </c>
       <c r="B34" t="n">
         <v>79260</v>
@@ -3894,10 +3889,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454246</v>
+        <v>454233</v>
       </c>
       <c r="R34" t="n">
-        <v>6762660</v>
+        <v>6762667</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3956,10 +3951,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131700019</v>
+        <v>131700614</v>
       </c>
       <c r="B35" t="n">
-        <v>79260</v>
+        <v>79850</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3967,21 +3962,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3991,10 +3986,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454460</v>
+        <v>454380</v>
       </c>
       <c r="R35" t="n">
-        <v>6762684</v>
+        <v>6762722</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4053,45 +4048,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131704692</v>
+        <v>131699709</v>
       </c>
       <c r="B36" t="n">
-        <v>79260</v>
+        <v>8453</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454233</v>
+        <v>454510</v>
       </c>
       <c r="R36" t="n">
-        <v>6762667</v>
+        <v>6762678</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4150,50 +4150,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131699571</v>
+        <v>131699483</v>
       </c>
       <c r="B37" t="n">
-        <v>8453</v>
+        <v>79260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454487</v>
+        <v>454462</v>
       </c>
       <c r="R37" t="n">
-        <v>6762659</v>
+        <v>6762674</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4349,45 +4344,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131699483</v>
+        <v>131699571</v>
       </c>
       <c r="B39" t="n">
-        <v>79260</v>
+        <v>8453</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454462</v>
+        <v>454487</v>
       </c>
       <c r="R39" t="n">
-        <v>6762674</v>
+        <v>6762659</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4446,7 +4446,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131699577</v>
+        <v>131703843</v>
       </c>
       <c r="B40" t="n">
         <v>79260</v>
@@ -4481,13 +4481,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454487</v>
+        <v>454311</v>
       </c>
       <c r="R40" t="n">
-        <v>6762659</v>
+        <v>6762631</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4517,6 +4517,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4645,10 +4650,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131703843</v>
+        <v>131704203</v>
       </c>
       <c r="B42" t="n">
-        <v>79260</v>
+        <v>57895</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4656,37 +4661,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454311</v>
+        <v>454293</v>
       </c>
       <c r="R42" t="n">
-        <v>6762631</v>
+        <v>6762667</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4716,11 +4726,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4747,10 +4752,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131704203</v>
+        <v>131699577</v>
       </c>
       <c r="B43" t="n">
-        <v>57895</v>
+        <v>79260</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4758,39 +4763,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454293</v>
+        <v>454487</v>
       </c>
       <c r="R43" t="n">
-        <v>6762667</v>
+        <v>6762659</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 7951-2026 artfynd.xlsx
+++ b/artfynd/A 7951-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131703046</v>
       </c>
       <c r="B2" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131701230</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131704892</v>
+        <v>131699481</v>
       </c>
       <c r="B4" t="n">
-        <v>79879</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454246</v>
+        <v>454462</v>
       </c>
       <c r="R4" t="n">
-        <v>6762660</v>
+        <v>6762674</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131699481</v>
+        <v>131698769</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,7 +1002,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454462</v>
+        <v>454359</v>
       </c>
       <c r="R5" t="n">
-        <v>6762674</v>
+        <v>6762685</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131698769</v>
+        <v>131704892</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>79880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,39 +1084,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454359</v>
+        <v>454246</v>
       </c>
       <c r="R6" t="n">
-        <v>6762685</v>
+        <v>6762660</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131700972</v>
+        <v>131700622</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>79880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,39 +1181,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454349</v>
+        <v>454380</v>
       </c>
       <c r="R7" t="n">
-        <v>6762723</v>
+        <v>6762722</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131700622</v>
+        <v>131700907</v>
       </c>
       <c r="B8" t="n">
-        <v>79879</v>
+        <v>79261</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,13 +1302,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454380</v>
+        <v>454348</v>
       </c>
       <c r="R8" t="n">
-        <v>6762722</v>
+        <v>6762712</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1343,6 +1338,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1369,10 +1369,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131700907</v>
+        <v>131700972</v>
       </c>
       <c r="B9" t="n">
-        <v>79260</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1380,37 +1380,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454348</v>
+        <v>454349</v>
       </c>
       <c r="R9" t="n">
-        <v>6762712</v>
+        <v>6762723</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1440,11 +1445,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1474,7 +1474,7 @@
         <v>131702441</v>
       </c>
       <c r="B10" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>131704688</v>
       </c>
       <c r="B11" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,50 +1680,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131701172</v>
+        <v>131698785</v>
       </c>
       <c r="B12" t="n">
-        <v>8453</v>
+        <v>79261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454329</v>
+        <v>454359</v>
       </c>
       <c r="R12" t="n">
-        <v>6762746</v>
+        <v>6762685</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,7 +1780,7 @@
         <v>131699170</v>
       </c>
       <c r="B13" t="n">
-        <v>8453</v>
+        <v>8454</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1884,45 +1879,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131698785</v>
+        <v>131701172</v>
       </c>
       <c r="B14" t="n">
-        <v>79260</v>
+        <v>8454</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454359</v>
+        <v>454329</v>
       </c>
       <c r="R14" t="n">
-        <v>6762685</v>
+        <v>6762746</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1984,7 +1984,7 @@
         <v>131699324</v>
       </c>
       <c r="B15" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>131699011</v>
       </c>
       <c r="B16" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>131701058</v>
       </c>
       <c r="B17" t="n">
-        <v>79850</v>
+        <v>79851</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2277,45 +2277,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131700625</v>
+        <v>131700699</v>
       </c>
       <c r="B18" t="n">
-        <v>79260</v>
+        <v>8454</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454380</v>
+        <v>454367</v>
       </c>
       <c r="R18" t="n">
-        <v>6762722</v>
+        <v>6762713</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2374,50 +2379,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131700699</v>
+        <v>131700625</v>
       </c>
       <c r="B19" t="n">
-        <v>8453</v>
+        <v>79261</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454367</v>
+        <v>454380</v>
       </c>
       <c r="R19" t="n">
-        <v>6762713</v>
+        <v>6762722</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2479,7 +2479,7 @@
         <v>131704301</v>
       </c>
       <c r="B20" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>131699864</v>
       </c>
       <c r="B21" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>131701072</v>
       </c>
       <c r="B22" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>131699226</v>
       </c>
       <c r="B23" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>131701061</v>
       </c>
       <c r="B24" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>131704207</v>
       </c>
       <c r="B25" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>131700974</v>
       </c>
       <c r="B26" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>131699230</v>
       </c>
       <c r="B27" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>131700143</v>
       </c>
       <c r="B28" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3364,10 +3364,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131704877</v>
+        <v>131704612</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>79261</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3375,21 +3375,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454246</v>
+        <v>454234</v>
       </c>
       <c r="R29" t="n">
-        <v>6762660</v>
+        <v>6762699</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3461,10 +3461,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131704612</v>
+        <v>131701164</v>
       </c>
       <c r="B30" t="n">
-        <v>79260</v>
+        <v>57896</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3472,34 +3472,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454234</v>
+        <v>454329</v>
       </c>
       <c r="R30" t="n">
-        <v>6762699</v>
+        <v>6762746</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3558,10 +3563,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131701164</v>
+        <v>131704877</v>
       </c>
       <c r="B31" t="n">
-        <v>57895</v>
+        <v>79019</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3569,39 +3574,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454329</v>
+        <v>454246</v>
       </c>
       <c r="R31" t="n">
-        <v>6762746</v>
+        <v>6762660</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3660,45 +3660,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131704895</v>
+        <v>131699709</v>
       </c>
       <c r="B32" t="n">
-        <v>79260</v>
+        <v>8454</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454246</v>
+        <v>454510</v>
       </c>
       <c r="R32" t="n">
-        <v>6762660</v>
+        <v>6762678</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3757,10 +3762,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131700019</v>
+        <v>131700614</v>
       </c>
       <c r="B33" t="n">
-        <v>79260</v>
+        <v>79851</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3768,21 +3773,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3792,10 +3797,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454460</v>
+        <v>454380</v>
       </c>
       <c r="R33" t="n">
-        <v>6762684</v>
+        <v>6762722</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3854,10 +3859,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131704692</v>
+        <v>131704895</v>
       </c>
       <c r="B34" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3889,10 +3894,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454233</v>
+        <v>454246</v>
       </c>
       <c r="R34" t="n">
-        <v>6762667</v>
+        <v>6762660</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3951,10 +3956,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131700614</v>
+        <v>131700019</v>
       </c>
       <c r="B35" t="n">
-        <v>79850</v>
+        <v>79261</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3962,21 +3967,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3986,10 +3991,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454380</v>
+        <v>454460</v>
       </c>
       <c r="R35" t="n">
-        <v>6762722</v>
+        <v>6762684</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4048,50 +4053,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131699709</v>
+        <v>131704692</v>
       </c>
       <c r="B36" t="n">
-        <v>8453</v>
+        <v>79261</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454510</v>
+        <v>454233</v>
       </c>
       <c r="R36" t="n">
-        <v>6762678</v>
+        <v>6762667</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4153,7 +4153,7 @@
         <v>131699483</v>
       </c>
       <c r="B37" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>131699721</v>
       </c>
       <c r="B38" t="n">
-        <v>79261</v>
+        <v>79262</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>131699571</v>
       </c>
       <c r="B39" t="n">
-        <v>8453</v>
+        <v>8454</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4446,10 +4446,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131703843</v>
+        <v>131699577</v>
       </c>
       <c r="B40" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4481,13 +4481,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454311</v>
+        <v>454487</v>
       </c>
       <c r="R40" t="n">
-        <v>6762631</v>
+        <v>6762659</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4517,11 +4517,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4548,10 +4543,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131703645</v>
+        <v>131703843</v>
       </c>
       <c r="B41" t="n">
-        <v>57898</v>
+        <v>79261</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4559,42 +4554,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454323</v>
+        <v>454311</v>
       </c>
       <c r="R41" t="n">
-        <v>6762672</v>
+        <v>6762631</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4624,6 +4614,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4650,10 +4645,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131704203</v>
+        <v>131703645</v>
       </c>
       <c r="B42" t="n">
-        <v>57895</v>
+        <v>57899</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4661,16 +4656,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4690,10 +4685,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454293</v>
+        <v>454323</v>
       </c>
       <c r="R42" t="n">
-        <v>6762667</v>
+        <v>6762672</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4752,10 +4747,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131699577</v>
+        <v>131704203</v>
       </c>
       <c r="B43" t="n">
-        <v>79260</v>
+        <v>57896</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4763,34 +4758,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454487</v>
+        <v>454293</v>
       </c>
       <c r="R43" t="n">
-        <v>6762659</v>
+        <v>6762667</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4852,7 +4852,7 @@
         <v>131701249</v>
       </c>
       <c r="B44" t="n">
-        <v>8453</v>
+        <v>8454</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>131698930</v>
       </c>
       <c r="B45" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 7951-2026 artfynd.xlsx
+++ b/artfynd/A 7951-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131703046</v>
       </c>
       <c r="B2" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131701230</v>
       </c>
       <c r="B3" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131699481</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>131698769</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>131704892</v>
       </c>
       <c r="B6" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131700622</v>
+        <v>131700972</v>
       </c>
       <c r="B7" t="n">
-        <v>79880</v>
+        <v>57902</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,34 +1181,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454380</v>
+        <v>454349</v>
       </c>
       <c r="R7" t="n">
-        <v>6762722</v>
+        <v>6762723</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,7 +1275,7 @@
         <v>131700907</v>
       </c>
       <c r="B8" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131700972</v>
+        <v>131700622</v>
       </c>
       <c r="B9" t="n">
-        <v>57899</v>
+        <v>79883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1380,39 +1385,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454349</v>
+        <v>454380</v>
       </c>
       <c r="R9" t="n">
-        <v>6762723</v>
+        <v>6762722</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1474,7 +1474,7 @@
         <v>131702441</v>
       </c>
       <c r="B10" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>131704688</v>
       </c>
       <c r="B11" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>131698785</v>
       </c>
       <c r="B12" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>131699324</v>
       </c>
       <c r="B15" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2078,10 +2078,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131699011</v>
+        <v>131701058</v>
       </c>
       <c r="B16" t="n">
-        <v>57896</v>
+        <v>79854</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2089,39 +2089,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454431</v>
+        <v>454329</v>
       </c>
       <c r="R16" t="n">
-        <v>6762675</v>
+        <v>6762746</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2180,10 +2175,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131701058</v>
+        <v>131699011</v>
       </c>
       <c r="B17" t="n">
-        <v>79851</v>
+        <v>57899</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,34 +2186,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454329</v>
+        <v>454431</v>
       </c>
       <c r="R17" t="n">
-        <v>6762746</v>
+        <v>6762675</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2277,50 +2277,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131700699</v>
+        <v>131700625</v>
       </c>
       <c r="B18" t="n">
-        <v>8454</v>
+        <v>79264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454367</v>
+        <v>454380</v>
       </c>
       <c r="R18" t="n">
-        <v>6762713</v>
+        <v>6762722</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2379,45 +2374,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131700625</v>
+        <v>131700699</v>
       </c>
       <c r="B19" t="n">
-        <v>79261</v>
+        <v>8454</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454380</v>
+        <v>454367</v>
       </c>
       <c r="R19" t="n">
-        <v>6762722</v>
+        <v>6762713</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2476,10 +2476,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131704301</v>
+        <v>131699864</v>
       </c>
       <c r="B20" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454291</v>
+        <v>454488</v>
       </c>
       <c r="R20" t="n">
-        <v>6762688</v>
+        <v>6762699</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,6 +2547,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Miljöbilder och garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2573,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131699864</v>
+        <v>131704301</v>
       </c>
       <c r="B21" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2608,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454488</v>
+        <v>454291</v>
       </c>
       <c r="R21" t="n">
-        <v>6762699</v>
+        <v>6762688</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2644,11 +2649,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Miljöbilder och garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2678,7 +2678,7 @@
         <v>131701072</v>
       </c>
       <c r="B22" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>131699226</v>
       </c>
       <c r="B23" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131701061</v>
+        <v>131704207</v>
       </c>
       <c r="B24" t="n">
-        <v>79880</v>
+        <v>79264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2885,21 +2885,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454329</v>
+        <v>454293</v>
       </c>
       <c r="R24" t="n">
-        <v>6762746</v>
+        <v>6762667</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2971,10 +2971,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131704207</v>
+        <v>131700974</v>
       </c>
       <c r="B25" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,10 +3006,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454293</v>
+        <v>454349</v>
       </c>
       <c r="R25" t="n">
-        <v>6762667</v>
+        <v>6762723</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3068,10 +3068,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131700974</v>
+        <v>131701061</v>
       </c>
       <c r="B26" t="n">
-        <v>79261</v>
+        <v>79883</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3079,21 +3079,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454349</v>
+        <v>454329</v>
       </c>
       <c r="R26" t="n">
-        <v>6762723</v>
+        <v>6762746</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3165,10 +3165,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131699230</v>
+        <v>131700143</v>
       </c>
       <c r="B27" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454445</v>
+        <v>454452</v>
       </c>
       <c r="R27" t="n">
-        <v>6762675</v>
+        <v>6762716</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3236,6 +3236,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt med garnlav i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3262,10 +3267,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131700143</v>
+        <v>131699230</v>
       </c>
       <c r="B28" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3297,13 +3302,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454452</v>
+        <v>454445</v>
       </c>
       <c r="R28" t="n">
-        <v>6762716</v>
+        <v>6762675</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3333,11 +3338,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt med garnlav i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3367,7 +3367,7 @@
         <v>131704612</v>
       </c>
       <c r="B29" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>131701164</v>
       </c>
       <c r="B30" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>131704877</v>
       </c>
       <c r="B31" t="n">
-        <v>79019</v>
+        <v>79022</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>131700614</v>
       </c>
       <c r="B33" t="n">
-        <v>79851</v>
+        <v>79854</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>131704895</v>
       </c>
       <c r="B34" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>131700019</v>
       </c>
       <c r="B35" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>131704692</v>
       </c>
       <c r="B36" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>131699483</v>
       </c>
       <c r="B37" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4247,45 +4247,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131699721</v>
+        <v>131699571</v>
       </c>
       <c r="B38" t="n">
-        <v>79262</v>
+        <v>8454</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>230405</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454510</v>
+        <v>454487</v>
       </c>
       <c r="R38" t="n">
-        <v>6762678</v>
+        <v>6762659</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4344,50 +4349,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131699571</v>
+        <v>131699721</v>
       </c>
       <c r="B39" t="n">
-        <v>8454</v>
+        <v>79265</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>230405</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454487</v>
+        <v>454510</v>
       </c>
       <c r="R39" t="n">
-        <v>6762659</v>
+        <v>6762678</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4446,10 +4446,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131699577</v>
+        <v>131703843</v>
       </c>
       <c r="B40" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4481,13 +4481,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454487</v>
+        <v>454311</v>
       </c>
       <c r="R40" t="n">
-        <v>6762659</v>
+        <v>6762631</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4517,6 +4517,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4543,10 +4548,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131703843</v>
+        <v>131704203</v>
       </c>
       <c r="B41" t="n">
-        <v>79261</v>
+        <v>57899</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4554,37 +4559,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454311</v>
+        <v>454293</v>
       </c>
       <c r="R41" t="n">
-        <v>6762631</v>
+        <v>6762667</v>
       </c>
       <c r="S41" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4614,11 +4624,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4648,7 +4653,7 @@
         <v>131703645</v>
       </c>
       <c r="B42" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4747,10 +4752,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131704203</v>
+        <v>131699577</v>
       </c>
       <c r="B43" t="n">
-        <v>57896</v>
+        <v>79264</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4758,39 +4763,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454293</v>
+        <v>454487</v>
       </c>
       <c r="R43" t="n">
-        <v>6762667</v>
+        <v>6762659</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4954,7 +4954,7 @@
         <v>131698930</v>
       </c>
       <c r="B45" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 7951-2026 artfynd.xlsx
+++ b/artfynd/A 7951-2026 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131699481</v>
+        <v>131704892</v>
       </c>
       <c r="B4" t="n">
-        <v>57902</v>
+        <v>79883</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,39 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454462</v>
+        <v>454246</v>
       </c>
       <c r="R4" t="n">
-        <v>6762674</v>
+        <v>6762660</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131698769</v>
+        <v>131699481</v>
       </c>
       <c r="B5" t="n">
         <v>57902</v>
@@ -1002,7 +997,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454359</v>
+        <v>454462</v>
       </c>
       <c r="R5" t="n">
-        <v>6762685</v>
+        <v>6762674</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131704892</v>
+        <v>131698769</v>
       </c>
       <c r="B6" t="n">
-        <v>79883</v>
+        <v>57902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,34 +1079,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454246</v>
+        <v>454359</v>
       </c>
       <c r="R6" t="n">
-        <v>6762660</v>
+        <v>6762685</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131700972</v>
+        <v>131700622</v>
       </c>
       <c r="B7" t="n">
-        <v>57902</v>
+        <v>79883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,39 +1181,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454349</v>
+        <v>454380</v>
       </c>
       <c r="R7" t="n">
-        <v>6762723</v>
+        <v>6762722</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131700907</v>
+        <v>131700972</v>
       </c>
       <c r="B8" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,37 +1278,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454348</v>
+        <v>454349</v>
       </c>
       <c r="R8" t="n">
-        <v>6762712</v>
+        <v>6762723</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1343,11 +1343,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,10 +1369,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131700622</v>
+        <v>131700907</v>
       </c>
       <c r="B9" t="n">
-        <v>79883</v>
+        <v>79264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1380,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,13 +1404,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454380</v>
+        <v>454348</v>
       </c>
       <c r="R9" t="n">
-        <v>6762722</v>
+        <v>6762712</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1445,6 +1440,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1680,45 +1680,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131698785</v>
+        <v>131701172</v>
       </c>
       <c r="B12" t="n">
-        <v>79264</v>
+        <v>8454</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454359</v>
+        <v>454329</v>
       </c>
       <c r="R12" t="n">
-        <v>6762685</v>
+        <v>6762746</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,50 +1782,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131699170</v>
+        <v>131698785</v>
       </c>
       <c r="B13" t="n">
-        <v>8454</v>
+        <v>79264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454431</v>
+        <v>454359</v>
       </c>
       <c r="R13" t="n">
-        <v>6762675</v>
+        <v>6762685</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131701172</v>
+        <v>131699170</v>
       </c>
       <c r="B14" t="n">
         <v>8454</v>
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454329</v>
+        <v>454431</v>
       </c>
       <c r="R14" t="n">
-        <v>6762746</v>
+        <v>6762675</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131701072</v>
+        <v>131699226</v>
       </c>
       <c r="B22" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,34 +2686,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454329</v>
+        <v>454445</v>
       </c>
       <c r="R22" t="n">
-        <v>6762746</v>
+        <v>6762675</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2772,10 +2777,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131699226</v>
+        <v>131701072</v>
       </c>
       <c r="B23" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2783,39 +2788,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454445</v>
+        <v>454329</v>
       </c>
       <c r="R23" t="n">
-        <v>6762675</v>
+        <v>6762746</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3165,7 +3165,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131700143</v>
+        <v>131699230</v>
       </c>
       <c r="B27" t="n">
         <v>79264</v>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454452</v>
+        <v>454445</v>
       </c>
       <c r="R27" t="n">
-        <v>6762716</v>
+        <v>6762675</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3236,11 +3236,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt med garnlav i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3267,7 +3262,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131699230</v>
+        <v>131700143</v>
       </c>
       <c r="B28" t="n">
         <v>79264</v>
@@ -3302,13 +3297,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454445</v>
+        <v>454452</v>
       </c>
       <c r="R28" t="n">
-        <v>6762675</v>
+        <v>6762716</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3338,6 +3333,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt med garnlav i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3461,10 +3461,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131701164</v>
+        <v>131704877</v>
       </c>
       <c r="B30" t="n">
-        <v>57899</v>
+        <v>79022</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3472,39 +3472,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454329</v>
+        <v>454246</v>
       </c>
       <c r="R30" t="n">
-        <v>6762746</v>
+        <v>6762660</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3563,10 +3558,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131704877</v>
+        <v>131701164</v>
       </c>
       <c r="B31" t="n">
-        <v>79022</v>
+        <v>57899</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3574,34 +3569,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454246</v>
+        <v>454329</v>
       </c>
       <c r="R31" t="n">
-        <v>6762660</v>
+        <v>6762746</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3660,50 +3660,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131699709</v>
+        <v>131700614</v>
       </c>
       <c r="B32" t="n">
-        <v>8454</v>
+        <v>79854</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454510</v>
+        <v>454380</v>
       </c>
       <c r="R32" t="n">
-        <v>6762678</v>
+        <v>6762722</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3762,45 +3757,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131700614</v>
+        <v>131699709</v>
       </c>
       <c r="B33" t="n">
-        <v>79854</v>
+        <v>8454</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454380</v>
+        <v>454510</v>
       </c>
       <c r="R33" t="n">
-        <v>6762722</v>
+        <v>6762678</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4548,10 +4548,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131704203</v>
+        <v>131699577</v>
       </c>
       <c r="B41" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4559,39 +4559,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454293</v>
+        <v>454487</v>
       </c>
       <c r="R41" t="n">
-        <v>6762667</v>
+        <v>6762659</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4650,10 +4645,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131703645</v>
+        <v>131704203</v>
       </c>
       <c r="B42" t="n">
-        <v>57902</v>
+        <v>57899</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4661,16 +4656,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4690,10 +4685,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454323</v>
+        <v>454293</v>
       </c>
       <c r="R42" t="n">
-        <v>6762672</v>
+        <v>6762667</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4752,10 +4747,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131699577</v>
+        <v>131703645</v>
       </c>
       <c r="B43" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4763,34 +4758,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454487</v>
+        <v>454323</v>
       </c>
       <c r="R43" t="n">
-        <v>6762659</v>
+        <v>6762672</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 7951-2026 artfynd.xlsx
+++ b/artfynd/A 7951-2026 artfynd.xlsx
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131700622</v>
+        <v>131700907</v>
       </c>
       <c r="B7" t="n">
-        <v>79883</v>
+        <v>79264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454380</v>
+        <v>454348</v>
       </c>
       <c r="R7" t="n">
-        <v>6762722</v>
+        <v>6762712</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1241,6 +1241,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131700972</v>
+        <v>131700622</v>
       </c>
       <c r="B8" t="n">
-        <v>57902</v>
+        <v>79883</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,39 +1283,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454349</v>
+        <v>454380</v>
       </c>
       <c r="R8" t="n">
-        <v>6762723</v>
+        <v>6762722</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1369,10 +1369,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131700907</v>
+        <v>131700972</v>
       </c>
       <c r="B9" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1380,37 +1380,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454348</v>
+        <v>454349</v>
       </c>
       <c r="R9" t="n">
-        <v>6762712</v>
+        <v>6762723</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1440,11 +1445,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2078,10 +2078,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131701058</v>
+        <v>131699011</v>
       </c>
       <c r="B16" t="n">
-        <v>79854</v>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2089,34 +2089,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454329</v>
+        <v>454431</v>
       </c>
       <c r="R16" t="n">
-        <v>6762746</v>
+        <v>6762675</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2175,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131699011</v>
+        <v>131701058</v>
       </c>
       <c r="B17" t="n">
-        <v>57899</v>
+        <v>79854</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2186,39 +2191,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454431</v>
+        <v>454329</v>
       </c>
       <c r="R17" t="n">
-        <v>6762675</v>
+        <v>6762746</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2277,45 +2277,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131700625</v>
+        <v>131700699</v>
       </c>
       <c r="B18" t="n">
-        <v>79264</v>
+        <v>8454</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454380</v>
+        <v>454367</v>
       </c>
       <c r="R18" t="n">
-        <v>6762722</v>
+        <v>6762713</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2374,50 +2379,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131700699</v>
+        <v>131700625</v>
       </c>
       <c r="B19" t="n">
-        <v>8454</v>
+        <v>79264</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454367</v>
+        <v>454380</v>
       </c>
       <c r="R19" t="n">
-        <v>6762713</v>
+        <v>6762722</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2476,7 +2476,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131699864</v>
+        <v>131704301</v>
       </c>
       <c r="B20" t="n">
         <v>79264</v>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454488</v>
+        <v>454291</v>
       </c>
       <c r="R20" t="n">
-        <v>6762699</v>
+        <v>6762688</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,11 +2547,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Miljöbilder och garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2578,7 +2573,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131704301</v>
+        <v>131699864</v>
       </c>
       <c r="B21" t="n">
         <v>79264</v>
@@ -2613,10 +2608,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454291</v>
+        <v>454488</v>
       </c>
       <c r="R21" t="n">
-        <v>6762688</v>
+        <v>6762699</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2649,6 +2644,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Miljöbilder och garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131699226</v>
+        <v>131701072</v>
       </c>
       <c r="B22" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,39 +2686,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454445</v>
+        <v>454329</v>
       </c>
       <c r="R22" t="n">
-        <v>6762675</v>
+        <v>6762746</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2777,10 +2772,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131701072</v>
+        <v>131699226</v>
       </c>
       <c r="B23" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2788,34 +2783,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454329</v>
+        <v>454445</v>
       </c>
       <c r="R23" t="n">
-        <v>6762746</v>
+        <v>6762675</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2874,7 +2874,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131704207</v>
+        <v>131700974</v>
       </c>
       <c r="B24" t="n">
         <v>79264</v>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454293</v>
+        <v>454349</v>
       </c>
       <c r="R24" t="n">
-        <v>6762667</v>
+        <v>6762723</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2971,10 +2971,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131700974</v>
+        <v>131701061</v>
       </c>
       <c r="B25" t="n">
-        <v>79264</v>
+        <v>79883</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2982,21 +2982,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3006,10 +3006,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454349</v>
+        <v>454329</v>
       </c>
       <c r="R25" t="n">
-        <v>6762723</v>
+        <v>6762746</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3068,10 +3068,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131701061</v>
+        <v>131704207</v>
       </c>
       <c r="B26" t="n">
-        <v>79883</v>
+        <v>79264</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3079,21 +3079,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454329</v>
+        <v>454293</v>
       </c>
       <c r="R26" t="n">
-        <v>6762746</v>
+        <v>6762667</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3165,7 +3165,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131699230</v>
+        <v>131700143</v>
       </c>
       <c r="B27" t="n">
         <v>79264</v>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454445</v>
+        <v>454452</v>
       </c>
       <c r="R27" t="n">
-        <v>6762675</v>
+        <v>6762716</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3236,6 +3236,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt med garnlav i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3262,7 +3267,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131700143</v>
+        <v>131699230</v>
       </c>
       <c r="B28" t="n">
         <v>79264</v>
@@ -3297,13 +3302,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454452</v>
+        <v>454445</v>
       </c>
       <c r="R28" t="n">
-        <v>6762716</v>
+        <v>6762675</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3333,11 +3338,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt med garnlav i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3364,10 +3364,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131704612</v>
+        <v>131701164</v>
       </c>
       <c r="B29" t="n">
-        <v>79264</v>
+        <v>57899</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3375,34 +3375,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454234</v>
+        <v>454329</v>
       </c>
       <c r="R29" t="n">
-        <v>6762699</v>
+        <v>6762746</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3558,10 +3563,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131701164</v>
+        <v>131704612</v>
       </c>
       <c r="B31" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3569,39 +3574,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454329</v>
+        <v>454234</v>
       </c>
       <c r="R31" t="n">
-        <v>6762746</v>
+        <v>6762699</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3660,10 +3660,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131700614</v>
+        <v>131700019</v>
       </c>
       <c r="B32" t="n">
-        <v>79854</v>
+        <v>79264</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3671,21 +3671,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454380</v>
+        <v>454460</v>
       </c>
       <c r="R32" t="n">
-        <v>6762722</v>
+        <v>6762684</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3757,50 +3757,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131699709</v>
+        <v>131704692</v>
       </c>
       <c r="B33" t="n">
-        <v>8454</v>
+        <v>79264</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454510</v>
+        <v>454233</v>
       </c>
       <c r="R33" t="n">
-        <v>6762678</v>
+        <v>6762667</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3956,10 +3951,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131700019</v>
+        <v>131700614</v>
       </c>
       <c r="B35" t="n">
-        <v>79264</v>
+        <v>79854</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3967,21 +3962,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3991,10 +3986,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454460</v>
+        <v>454380</v>
       </c>
       <c r="R35" t="n">
-        <v>6762684</v>
+        <v>6762722</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4053,45 +4048,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131704692</v>
+        <v>131699709</v>
       </c>
       <c r="B36" t="n">
-        <v>79264</v>
+        <v>8454</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454233</v>
+        <v>454510</v>
       </c>
       <c r="R36" t="n">
-        <v>6762667</v>
+        <v>6762678</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4446,10 +4446,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131703843</v>
+        <v>131703645</v>
       </c>
       <c r="B40" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4457,37 +4457,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454311</v>
+        <v>454323</v>
       </c>
       <c r="R40" t="n">
-        <v>6762631</v>
+        <v>6762672</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4517,11 +4522,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4548,10 +4548,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131699577</v>
+        <v>131704203</v>
       </c>
       <c r="B41" t="n">
-        <v>79264</v>
+        <v>57899</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4559,34 +4559,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454487</v>
+        <v>454293</v>
       </c>
       <c r="R41" t="n">
-        <v>6762659</v>
+        <v>6762667</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4645,10 +4650,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131704203</v>
+        <v>131703843</v>
       </c>
       <c r="B42" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4656,42 +4661,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454293</v>
+        <v>454311</v>
       </c>
       <c r="R42" t="n">
-        <v>6762667</v>
+        <v>6762631</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4721,6 +4721,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4747,10 +4752,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131703645</v>
+        <v>131699577</v>
       </c>
       <c r="B43" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4758,39 +4763,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454323</v>
+        <v>454487</v>
       </c>
       <c r="R43" t="n">
-        <v>6762672</v>
+        <v>6762659</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 7951-2026 artfynd.xlsx
+++ b/artfynd/A 7951-2026 artfynd.xlsx
@@ -1680,50 +1680,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131701172</v>
+        <v>131698785</v>
       </c>
       <c r="B12" t="n">
-        <v>8454</v>
+        <v>79264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454329</v>
+        <v>454359</v>
       </c>
       <c r="R12" t="n">
-        <v>6762746</v>
+        <v>6762685</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1782,45 +1777,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131698785</v>
+        <v>131699170</v>
       </c>
       <c r="B13" t="n">
-        <v>79264</v>
+        <v>8454</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454359</v>
+        <v>454431</v>
       </c>
       <c r="R13" t="n">
-        <v>6762685</v>
+        <v>6762675</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131699170</v>
+        <v>131701172</v>
       </c>
       <c r="B14" t="n">
         <v>8454</v>
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454431</v>
+        <v>454329</v>
       </c>
       <c r="R14" t="n">
-        <v>6762675</v>
+        <v>6762746</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131701072</v>
+        <v>131699226</v>
       </c>
       <c r="B22" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,34 +2686,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454329</v>
+        <v>454445</v>
       </c>
       <c r="R22" t="n">
-        <v>6762746</v>
+        <v>6762675</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2772,10 +2777,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131699226</v>
+        <v>131701072</v>
       </c>
       <c r="B23" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2783,39 +2788,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454445</v>
+        <v>454329</v>
       </c>
       <c r="R23" t="n">
-        <v>6762675</v>
+        <v>6762746</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3364,10 +3364,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131701164</v>
+        <v>131704612</v>
       </c>
       <c r="B29" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3375,39 +3375,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454329</v>
+        <v>454234</v>
       </c>
       <c r="R29" t="n">
-        <v>6762746</v>
+        <v>6762699</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3466,10 +3461,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131704877</v>
+        <v>131701164</v>
       </c>
       <c r="B30" t="n">
-        <v>79022</v>
+        <v>57899</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3477,34 +3472,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454246</v>
+        <v>454329</v>
       </c>
       <c r="R30" t="n">
-        <v>6762660</v>
+        <v>6762746</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3563,10 +3563,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131704612</v>
+        <v>131704877</v>
       </c>
       <c r="B31" t="n">
-        <v>79264</v>
+        <v>79022</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3574,21 +3574,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454234</v>
+        <v>454246</v>
       </c>
       <c r="R31" t="n">
-        <v>6762699</v>
+        <v>6762660</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 7951-2026 artfynd.xlsx
+++ b/artfynd/A 7951-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131703046</v>
       </c>
       <c r="B2" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131701230</v>
       </c>
       <c r="B3" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>131704892</v>
       </c>
       <c r="B4" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>131699481</v>
       </c>
       <c r="B5" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>131698769</v>
       </c>
       <c r="B6" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>131700907</v>
       </c>
       <c r="B7" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>131700622</v>
       </c>
       <c r="B8" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>131700972</v>
       </c>
       <c r="B9" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>131702441</v>
       </c>
       <c r="B10" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>131704688</v>
       </c>
       <c r="B11" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>131698785</v>
       </c>
       <c r="B12" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>131699324</v>
       </c>
       <c r="B15" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>131699011</v>
       </c>
       <c r="B16" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>131701058</v>
       </c>
       <c r="B17" t="n">
-        <v>79854</v>
+        <v>79856</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>131700625</v>
       </c>
       <c r="B19" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>131704301</v>
       </c>
       <c r="B20" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>131699864</v>
       </c>
       <c r="B21" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131699226</v>
+        <v>131701072</v>
       </c>
       <c r="B22" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,39 +2686,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454445</v>
+        <v>454329</v>
       </c>
       <c r="R22" t="n">
-        <v>6762675</v>
+        <v>6762746</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2777,10 +2772,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131701072</v>
+        <v>131699226</v>
       </c>
       <c r="B23" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2788,34 +2783,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454329</v>
+        <v>454445</v>
       </c>
       <c r="R23" t="n">
-        <v>6762746</v>
+        <v>6762675</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131700974</v>
+        <v>131704207</v>
       </c>
       <c r="B24" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454349</v>
+        <v>454293</v>
       </c>
       <c r="R24" t="n">
-        <v>6762723</v>
+        <v>6762667</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2971,10 +2971,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131701061</v>
+        <v>131700974</v>
       </c>
       <c r="B25" t="n">
-        <v>79883</v>
+        <v>79266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2982,21 +2982,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3006,10 +3006,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454329</v>
+        <v>454349</v>
       </c>
       <c r="R25" t="n">
-        <v>6762746</v>
+        <v>6762723</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3068,10 +3068,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131704207</v>
+        <v>131701061</v>
       </c>
       <c r="B26" t="n">
-        <v>79264</v>
+        <v>79885</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3079,21 +3079,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454293</v>
+        <v>454329</v>
       </c>
       <c r="R26" t="n">
-        <v>6762667</v>
+        <v>6762746</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3165,10 +3165,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131700143</v>
+        <v>131699230</v>
       </c>
       <c r="B27" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454452</v>
+        <v>454445</v>
       </c>
       <c r="R27" t="n">
-        <v>6762716</v>
+        <v>6762675</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3236,11 +3236,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt med garnlav i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3267,10 +3262,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131699230</v>
+        <v>131700143</v>
       </c>
       <c r="B28" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3302,13 +3297,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454445</v>
+        <v>454452</v>
       </c>
       <c r="R28" t="n">
-        <v>6762675</v>
+        <v>6762716</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3338,6 +3333,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt med garnlav i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3364,10 +3364,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131704612</v>
+        <v>131701164</v>
       </c>
       <c r="B29" t="n">
-        <v>79264</v>
+        <v>57901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3375,34 +3375,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454234</v>
+        <v>454329</v>
       </c>
       <c r="R29" t="n">
-        <v>6762699</v>
+        <v>6762746</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3461,10 +3466,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131701164</v>
+        <v>131704877</v>
       </c>
       <c r="B30" t="n">
-        <v>57899</v>
+        <v>79024</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3472,39 +3477,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454329</v>
+        <v>454246</v>
       </c>
       <c r="R30" t="n">
-        <v>6762746</v>
+        <v>6762660</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3563,10 +3563,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131704877</v>
+        <v>131704612</v>
       </c>
       <c r="B31" t="n">
-        <v>79022</v>
+        <v>79266</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3574,21 +3574,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454246</v>
+        <v>454234</v>
       </c>
       <c r="R31" t="n">
-        <v>6762660</v>
+        <v>6762699</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3660,10 +3660,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131700019</v>
+        <v>131704895</v>
       </c>
       <c r="B32" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454460</v>
+        <v>454246</v>
       </c>
       <c r="R32" t="n">
-        <v>6762684</v>
+        <v>6762660</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3757,10 +3757,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131704692</v>
+        <v>131700019</v>
       </c>
       <c r="B33" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454233</v>
+        <v>454460</v>
       </c>
       <c r="R33" t="n">
-        <v>6762667</v>
+        <v>6762684</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3854,10 +3854,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131704895</v>
+        <v>131704692</v>
       </c>
       <c r="B34" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3889,10 +3889,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454246</v>
+        <v>454233</v>
       </c>
       <c r="R34" t="n">
-        <v>6762660</v>
+        <v>6762667</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3951,45 +3951,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131700614</v>
+        <v>131699709</v>
       </c>
       <c r="B35" t="n">
-        <v>79854</v>
+        <v>8454</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454380</v>
+        <v>454510</v>
       </c>
       <c r="R35" t="n">
-        <v>6762722</v>
+        <v>6762678</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4048,50 +4053,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131699709</v>
+        <v>131700614</v>
       </c>
       <c r="B36" t="n">
-        <v>8454</v>
+        <v>79856</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454510</v>
+        <v>454380</v>
       </c>
       <c r="R36" t="n">
-        <v>6762678</v>
+        <v>6762722</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4150,45 +4150,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131699483</v>
+        <v>131699571</v>
       </c>
       <c r="B37" t="n">
-        <v>79264</v>
+        <v>8454</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454462</v>
+        <v>454487</v>
       </c>
       <c r="R37" t="n">
-        <v>6762674</v>
+        <v>6762659</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4247,50 +4252,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131699571</v>
+        <v>131699721</v>
       </c>
       <c r="B38" t="n">
-        <v>8454</v>
+        <v>79267</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>230405</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454487</v>
+        <v>454510</v>
       </c>
       <c r="R38" t="n">
-        <v>6762659</v>
+        <v>6762678</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4349,10 +4349,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131699721</v>
+        <v>131699483</v>
       </c>
       <c r="B39" t="n">
-        <v>79265</v>
+        <v>79266</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4360,16 +4360,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454510</v>
+        <v>454462</v>
       </c>
       <c r="R39" t="n">
-        <v>6762678</v>
+        <v>6762674</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4446,10 +4446,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131703645</v>
+        <v>131699577</v>
       </c>
       <c r="B40" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4457,39 +4457,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454323</v>
+        <v>454487</v>
       </c>
       <c r="R40" t="n">
-        <v>6762672</v>
+        <v>6762659</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4551,7 +4546,7 @@
         <v>131704203</v>
       </c>
       <c r="B41" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4650,10 +4645,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131703843</v>
+        <v>131703645</v>
       </c>
       <c r="B42" t="n">
-        <v>79264</v>
+        <v>57904</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4661,37 +4656,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454311</v>
+        <v>454323</v>
       </c>
       <c r="R42" t="n">
-        <v>6762631</v>
+        <v>6762672</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4721,11 +4721,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4752,10 +4747,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131699577</v>
+        <v>131703843</v>
       </c>
       <c r="B43" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4787,13 +4782,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454487</v>
+        <v>454311</v>
       </c>
       <c r="R43" t="n">
-        <v>6762659</v>
+        <v>6762631</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4823,6 +4818,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4954,7 +4954,7 @@
         <v>131698930</v>
       </c>
       <c r="B45" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 7951-2026 artfynd.xlsx
+++ b/artfynd/A 7951-2026 artfynd.xlsx
@@ -1471,48 +1471,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131702441</v>
+        <v>131704688</v>
       </c>
       <c r="B10" t="n">
-        <v>79266</v>
+        <v>57092</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454300</v>
+        <v>454233</v>
       </c>
       <c r="R10" t="n">
-        <v>6762775</v>
+        <v>6762667</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1546,7 +1551,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
+          <t>Under tjädertall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,53 +1578,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131704688</v>
+        <v>131702441</v>
       </c>
       <c r="B11" t="n">
-        <v>57092</v>
+        <v>79266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454233</v>
+        <v>454300</v>
       </c>
       <c r="R11" t="n">
-        <v>6762667</v>
+        <v>6762775</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Under tjädertall</t>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131701072</v>
+        <v>131699226</v>
       </c>
       <c r="B22" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,34 +2686,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454329</v>
+        <v>454445</v>
       </c>
       <c r="R22" t="n">
-        <v>6762746</v>
+        <v>6762675</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2772,10 +2777,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131699226</v>
+        <v>131701072</v>
       </c>
       <c r="B23" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2783,39 +2788,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454445</v>
+        <v>454329</v>
       </c>
       <c r="R23" t="n">
-        <v>6762675</v>
+        <v>6762746</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 7951-2026 artfynd.xlsx
+++ b/artfynd/A 7951-2026 artfynd.xlsx
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131700907</v>
+        <v>131700972</v>
       </c>
       <c r="B7" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,37 +1181,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454348</v>
+        <v>454349</v>
       </c>
       <c r="R7" t="n">
-        <v>6762712</v>
+        <v>6762723</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1241,11 +1246,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131700622</v>
+        <v>131700907</v>
       </c>
       <c r="B8" t="n">
-        <v>79885</v>
+        <v>79266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1283,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454380</v>
+        <v>454348</v>
       </c>
       <c r="R8" t="n">
-        <v>6762722</v>
+        <v>6762712</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1343,6 +1343,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1369,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131700972</v>
+        <v>131700622</v>
       </c>
       <c r="B9" t="n">
-        <v>57904</v>
+        <v>79885</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1380,39 +1385,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454349</v>
+        <v>454380</v>
       </c>
       <c r="R9" t="n">
-        <v>6762723</v>
+        <v>6762722</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,53 +1471,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131704688</v>
+        <v>131702441</v>
       </c>
       <c r="B10" t="n">
-        <v>57092</v>
+        <v>79266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454233</v>
+        <v>454300</v>
       </c>
       <c r="R10" t="n">
-        <v>6762667</v>
+        <v>6762775</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1551,7 +1546,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Under tjädertall</t>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,48 +1573,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131702441</v>
+        <v>131704688</v>
       </c>
       <c r="B11" t="n">
-        <v>79266</v>
+        <v>57092</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454300</v>
+        <v>454233</v>
       </c>
       <c r="R11" t="n">
-        <v>6762775</v>
+        <v>6762667</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
+          <t>Under tjädertall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -4446,10 +4446,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131699577</v>
+        <v>131703645</v>
       </c>
       <c r="B40" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4457,34 +4457,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454487</v>
+        <v>454323</v>
       </c>
       <c r="R40" t="n">
-        <v>6762659</v>
+        <v>6762672</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4543,10 +4548,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131704203</v>
+        <v>131699577</v>
       </c>
       <c r="B41" t="n">
-        <v>57901</v>
+        <v>79266</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4554,39 +4559,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454293</v>
+        <v>454487</v>
       </c>
       <c r="R41" t="n">
-        <v>6762667</v>
+        <v>6762659</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4645,10 +4645,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131703645</v>
+        <v>131703843</v>
       </c>
       <c r="B42" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4656,42 +4656,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454323</v>
+        <v>454311</v>
       </c>
       <c r="R42" t="n">
-        <v>6762672</v>
+        <v>6762631</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4721,6 +4716,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4747,10 +4747,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131703843</v>
+        <v>131704203</v>
       </c>
       <c r="B43" t="n">
-        <v>79266</v>
+        <v>57901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4758,37 +4758,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454311</v>
+        <v>454293</v>
       </c>
       <c r="R43" t="n">
-        <v>6762631</v>
+        <v>6762667</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4818,11 +4823,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 7951-2026 artfynd.xlsx
+++ b/artfynd/A 7951-2026 artfynd.xlsx
@@ -1471,48 +1471,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131702441</v>
+        <v>131704688</v>
       </c>
       <c r="B10" t="n">
-        <v>79266</v>
+        <v>57092</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454300</v>
+        <v>454233</v>
       </c>
       <c r="R10" t="n">
-        <v>6762775</v>
+        <v>6762667</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1546,7 +1551,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
+          <t>Under tjädertall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,53 +1578,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131704688</v>
+        <v>131702441</v>
       </c>
       <c r="B11" t="n">
-        <v>57092</v>
+        <v>79266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454233</v>
+        <v>454300</v>
       </c>
       <c r="R11" t="n">
-        <v>6762667</v>
+        <v>6762775</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Under tjädertall</t>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2476,7 +2476,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131704301</v>
+        <v>131699864</v>
       </c>
       <c r="B20" t="n">
         <v>79266</v>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454291</v>
+        <v>454488</v>
       </c>
       <c r="R20" t="n">
-        <v>6762688</v>
+        <v>6762699</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,6 +2547,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Miljöbilder och garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2573,7 +2578,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131699864</v>
+        <v>131704301</v>
       </c>
       <c r="B21" t="n">
         <v>79266</v>
@@ -2608,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454488</v>
+        <v>454291</v>
       </c>
       <c r="R21" t="n">
-        <v>6762699</v>
+        <v>6762688</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2644,11 +2649,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Miljöbilder och garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4446,10 +4446,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131703645</v>
+        <v>131699577</v>
       </c>
       <c r="B40" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4457,39 +4457,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454323</v>
+        <v>454487</v>
       </c>
       <c r="R40" t="n">
-        <v>6762672</v>
+        <v>6762659</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4548,10 +4543,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131699577</v>
+        <v>131704203</v>
       </c>
       <c r="B41" t="n">
-        <v>79266</v>
+        <v>57901</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4559,34 +4554,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454487</v>
+        <v>454293</v>
       </c>
       <c r="R41" t="n">
-        <v>6762659</v>
+        <v>6762667</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4645,10 +4645,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131703843</v>
+        <v>131703645</v>
       </c>
       <c r="B42" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4656,37 +4656,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454311</v>
+        <v>454323</v>
       </c>
       <c r="R42" t="n">
-        <v>6762631</v>
+        <v>6762672</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4716,11 +4721,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4747,10 +4747,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131704203</v>
+        <v>131703843</v>
       </c>
       <c r="B43" t="n">
-        <v>57901</v>
+        <v>79266</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4758,42 +4758,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454293</v>
+        <v>454311</v>
       </c>
       <c r="R43" t="n">
-        <v>6762667</v>
+        <v>6762631</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4823,6 +4818,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 7951-2026 artfynd.xlsx
+++ b/artfynd/A 7951-2026 artfynd.xlsx
@@ -1471,53 +1471,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131704688</v>
+        <v>131702441</v>
       </c>
       <c r="B10" t="n">
-        <v>57092</v>
+        <v>79266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454233</v>
+        <v>454300</v>
       </c>
       <c r="R10" t="n">
-        <v>6762667</v>
+        <v>6762775</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1551,7 +1546,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Under tjädertall</t>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,48 +1573,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131702441</v>
+        <v>131704688</v>
       </c>
       <c r="B11" t="n">
-        <v>79266</v>
+        <v>57092</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454300</v>
+        <v>454233</v>
       </c>
       <c r="R11" t="n">
-        <v>6762775</v>
+        <v>6762667</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
+          <t>Under tjädertall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2476,7 +2476,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131699864</v>
+        <v>131704301</v>
       </c>
       <c r="B20" t="n">
         <v>79266</v>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454488</v>
+        <v>454291</v>
       </c>
       <c r="R20" t="n">
-        <v>6762699</v>
+        <v>6762688</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,11 +2547,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Miljöbilder och garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2578,7 +2573,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131704301</v>
+        <v>131699864</v>
       </c>
       <c r="B21" t="n">
         <v>79266</v>
@@ -2613,10 +2608,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454291</v>
+        <v>454488</v>
       </c>
       <c r="R21" t="n">
-        <v>6762688</v>
+        <v>6762699</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2649,6 +2644,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Miljöbilder och garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131699226</v>
+        <v>131701072</v>
       </c>
       <c r="B22" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,39 +2686,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454445</v>
+        <v>454329</v>
       </c>
       <c r="R22" t="n">
-        <v>6762675</v>
+        <v>6762746</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2777,10 +2772,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131701072</v>
+        <v>131699226</v>
       </c>
       <c r="B23" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2788,34 +2783,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454329</v>
+        <v>454445</v>
       </c>
       <c r="R23" t="n">
-        <v>6762746</v>
+        <v>6762675</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -4150,50 +4150,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131699571</v>
+        <v>131699483</v>
       </c>
       <c r="B37" t="n">
-        <v>8454</v>
+        <v>79266</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>454487</v>
+        <v>454462</v>
       </c>
       <c r="R37" t="n">
-        <v>6762659</v>
+        <v>6762674</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4252,45 +4247,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131699721</v>
+        <v>131699571</v>
       </c>
       <c r="B38" t="n">
-        <v>79267</v>
+        <v>8454</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>230405</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454510</v>
+        <v>454487</v>
       </c>
       <c r="R38" t="n">
-        <v>6762678</v>
+        <v>6762659</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4349,10 +4349,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131699483</v>
+        <v>131699721</v>
       </c>
       <c r="B39" t="n">
-        <v>79266</v>
+        <v>79267</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4360,16 +4360,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4384,10 +4384,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454462</v>
+        <v>454510</v>
       </c>
       <c r="R39" t="n">
-        <v>6762674</v>
+        <v>6762678</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 7951-2026 artfynd.xlsx
+++ b/artfynd/A 7951-2026 artfynd.xlsx
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131701072</v>
+        <v>131699226</v>
       </c>
       <c r="B22" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,34 +2686,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454329</v>
+        <v>454445</v>
       </c>
       <c r="R22" t="n">
-        <v>6762746</v>
+        <v>6762675</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2772,10 +2777,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131699226</v>
+        <v>131701072</v>
       </c>
       <c r="B23" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2783,39 +2788,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454445</v>
+        <v>454329</v>
       </c>
       <c r="R23" t="n">
-        <v>6762675</v>
+        <v>6762746</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 7951-2026 artfynd.xlsx
+++ b/artfynd/A 7951-2026 artfynd.xlsx
@@ -1471,48 +1471,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131702441</v>
+        <v>131704688</v>
       </c>
       <c r="B10" t="n">
-        <v>79266</v>
+        <v>57092</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454300</v>
+        <v>454233</v>
       </c>
       <c r="R10" t="n">
-        <v>6762775</v>
+        <v>6762667</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1546,7 +1551,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
+          <t>Under tjädertall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,53 +1578,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131704688</v>
+        <v>131702441</v>
       </c>
       <c r="B11" t="n">
-        <v>57092</v>
+        <v>79266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454233</v>
+        <v>454300</v>
       </c>
       <c r="R11" t="n">
-        <v>6762667</v>
+        <v>6762775</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Under tjädertall</t>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2476,7 +2476,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131704301</v>
+        <v>131699864</v>
       </c>
       <c r="B20" t="n">
         <v>79266</v>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454291</v>
+        <v>454488</v>
       </c>
       <c r="R20" t="n">
-        <v>6762688</v>
+        <v>6762699</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,6 +2547,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Miljöbilder och garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2573,7 +2578,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131699864</v>
+        <v>131704301</v>
       </c>
       <c r="B21" t="n">
         <v>79266</v>
@@ -2608,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454488</v>
+        <v>454291</v>
       </c>
       <c r="R21" t="n">
-        <v>6762699</v>
+        <v>6762688</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2644,11 +2649,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Miljöbilder och garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 7951-2026 artfynd.xlsx
+++ b/artfynd/A 7951-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131703046</v>
+        <v>131701230</v>
       </c>
       <c r="B2" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454349</v>
+        <v>454309</v>
       </c>
       <c r="R2" t="n">
-        <v>6762694</v>
+        <v>6762728</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131701230</v>
+        <v>131703046</v>
       </c>
       <c r="B3" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454309</v>
+        <v>454349</v>
       </c>
       <c r="R3" t="n">
-        <v>6762728</v>
+        <v>6762694</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131704892</v>
+        <v>131699481</v>
       </c>
       <c r="B4" t="n">
-        <v>79885</v>
+        <v>57907</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454246</v>
+        <v>454462</v>
       </c>
       <c r="R4" t="n">
-        <v>6762660</v>
+        <v>6762674</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131699481</v>
+        <v>131698769</v>
       </c>
       <c r="B5" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,7 +1002,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454462</v>
+        <v>454359</v>
       </c>
       <c r="R5" t="n">
-        <v>6762674</v>
+        <v>6762685</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131698769</v>
+        <v>131704892</v>
       </c>
       <c r="B6" t="n">
-        <v>57904</v>
+        <v>79888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,39 +1084,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454359</v>
+        <v>454246</v>
       </c>
       <c r="R6" t="n">
-        <v>6762685</v>
+        <v>6762660</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
         <v>131700972</v>
       </c>
       <c r="B7" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>131700907</v>
       </c>
       <c r="B8" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>131700622</v>
       </c>
       <c r="B9" t="n">
-        <v>79885</v>
+        <v>79888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>131704688</v>
       </c>
       <c r="B10" t="n">
-        <v>57092</v>
+        <v>57095</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>131702441</v>
       </c>
       <c r="B11" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,45 +1680,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131698785</v>
+        <v>131701172</v>
       </c>
       <c r="B12" t="n">
-        <v>79266</v>
+        <v>8455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454359</v>
+        <v>454329</v>
       </c>
       <c r="R12" t="n">
-        <v>6762685</v>
+        <v>6762746</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,50 +1782,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131699170</v>
+        <v>131698785</v>
       </c>
       <c r="B13" t="n">
-        <v>8454</v>
+        <v>79269</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454431</v>
+        <v>454359</v>
       </c>
       <c r="R13" t="n">
-        <v>6762675</v>
+        <v>6762685</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1879,10 +1879,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131701172</v>
+        <v>131699170</v>
       </c>
       <c r="B14" t="n">
-        <v>8454</v>
+        <v>8455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454329</v>
+        <v>454431</v>
       </c>
       <c r="R14" t="n">
-        <v>6762746</v>
+        <v>6762675</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1984,7 +1984,7 @@
         <v>131699324</v>
       </c>
       <c r="B15" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>131699011</v>
       </c>
       <c r="B16" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>131701058</v>
       </c>
       <c r="B17" t="n">
-        <v>79856</v>
+        <v>79859</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2277,50 +2277,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131700699</v>
+        <v>131700625</v>
       </c>
       <c r="B18" t="n">
-        <v>8454</v>
+        <v>79269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454367</v>
+        <v>454380</v>
       </c>
       <c r="R18" t="n">
-        <v>6762713</v>
+        <v>6762722</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2379,45 +2374,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131700625</v>
+        <v>131700699</v>
       </c>
       <c r="B19" t="n">
-        <v>79266</v>
+        <v>8455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454380</v>
+        <v>454367</v>
       </c>
       <c r="R19" t="n">
-        <v>6762722</v>
+        <v>6762713</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2476,10 +2476,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131699864</v>
+        <v>131704301</v>
       </c>
       <c r="B20" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454488</v>
+        <v>454291</v>
       </c>
       <c r="R20" t="n">
-        <v>6762699</v>
+        <v>6762688</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,11 +2547,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Miljöbilder och garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2578,10 +2573,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131704301</v>
+        <v>131699864</v>
       </c>
       <c r="B21" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2613,10 +2608,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454291</v>
+        <v>454488</v>
       </c>
       <c r="R21" t="n">
-        <v>6762688</v>
+        <v>6762699</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2649,6 +2644,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Miljöbilder och garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131699226</v>
+        <v>131701072</v>
       </c>
       <c r="B22" t="n">
-        <v>57904</v>
+        <v>79269</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,39 +2686,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454445</v>
+        <v>454329</v>
       </c>
       <c r="R22" t="n">
-        <v>6762675</v>
+        <v>6762746</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2777,10 +2772,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131701072</v>
+        <v>131699226</v>
       </c>
       <c r="B23" t="n">
-        <v>79266</v>
+        <v>57907</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2788,34 +2783,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454329</v>
+        <v>454445</v>
       </c>
       <c r="R23" t="n">
-        <v>6762746</v>
+        <v>6762675</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2877,7 +2877,7 @@
         <v>131704207</v>
       </c>
       <c r="B24" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>131700974</v>
       </c>
       <c r="B25" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>131701061</v>
       </c>
       <c r="B26" t="n">
-        <v>79885</v>
+        <v>79888</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>131699230</v>
       </c>
       <c r="B27" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>131700143</v>
       </c>
       <c r="B28" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3364,10 +3364,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131701164</v>
+        <v>131704612</v>
       </c>
       <c r="B29" t="n">
-        <v>57901</v>
+        <v>79269</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3375,39 +3375,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454329</v>
+        <v>454234</v>
       </c>
       <c r="R29" t="n">
-        <v>6762746</v>
+        <v>6762699</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3466,10 +3461,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131704877</v>
+        <v>131701164</v>
       </c>
       <c r="B30" t="n">
-        <v>79024</v>
+        <v>57904</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3477,34 +3472,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454246</v>
+        <v>454329</v>
       </c>
       <c r="R30" t="n">
-        <v>6762660</v>
+        <v>6762746</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3563,10 +3563,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131704612</v>
+        <v>131704877</v>
       </c>
       <c r="B31" t="n">
-        <v>79266</v>
+        <v>79027</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3574,21 +3574,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454234</v>
+        <v>454246</v>
       </c>
       <c r="R31" t="n">
-        <v>6762699</v>
+        <v>6762660</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3660,10 +3660,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131704895</v>
+        <v>131700614</v>
       </c>
       <c r="B32" t="n">
-        <v>79266</v>
+        <v>79859</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3671,21 +3671,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454246</v>
+        <v>454380</v>
       </c>
       <c r="R32" t="n">
-        <v>6762660</v>
+        <v>6762722</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3760,7 +3760,7 @@
         <v>131700019</v>
       </c>
       <c r="B33" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3854,10 +3854,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131704692</v>
+        <v>131704895</v>
       </c>
       <c r="B34" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3889,10 +3889,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454233</v>
+        <v>454246</v>
       </c>
       <c r="R34" t="n">
-        <v>6762667</v>
+        <v>6762660</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3951,50 +3951,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131699709</v>
+        <v>131704692</v>
       </c>
       <c r="B35" t="n">
-        <v>8454</v>
+        <v>79269</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454510</v>
+        <v>454233</v>
       </c>
       <c r="R35" t="n">
-        <v>6762678</v>
+        <v>6762667</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4053,45 +4048,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131700614</v>
+        <v>131699709</v>
       </c>
       <c r="B36" t="n">
-        <v>79856</v>
+        <v>8455</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454380</v>
+        <v>454510</v>
       </c>
       <c r="R36" t="n">
-        <v>6762722</v>
+        <v>6762678</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4153,7 +4153,7 @@
         <v>131699483</v>
       </c>
       <c r="B37" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>131699571</v>
       </c>
       <c r="B38" t="n">
-        <v>8454</v>
+        <v>8455</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>131699721</v>
       </c>
       <c r="B39" t="n">
-        <v>79267</v>
+        <v>79270</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4446,10 +4446,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131699577</v>
+        <v>131703843</v>
       </c>
       <c r="B40" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4481,13 +4481,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454487</v>
+        <v>454311</v>
       </c>
       <c r="R40" t="n">
-        <v>6762659</v>
+        <v>6762631</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4517,6 +4517,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4546,7 +4551,7 @@
         <v>131704203</v>
       </c>
       <c r="B41" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4648,7 +4653,7 @@
         <v>131703645</v>
       </c>
       <c r="B42" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4747,10 +4752,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131703843</v>
+        <v>131699577</v>
       </c>
       <c r="B43" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4782,13 +4787,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454311</v>
+        <v>454487</v>
       </c>
       <c r="R43" t="n">
-        <v>6762631</v>
+        <v>6762659</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4818,11 +4823,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4852,7 +4852,7 @@
         <v>131701249</v>
       </c>
       <c r="B44" t="n">
-        <v>8454</v>
+        <v>8455</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>131698930</v>
       </c>
       <c r="B45" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 7951-2026 artfynd.xlsx
+++ b/artfynd/A 7951-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131701230</v>
+        <v>131703046</v>
       </c>
       <c r="B2" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454309</v>
+        <v>454349</v>
       </c>
       <c r="R2" t="n">
-        <v>6762728</v>
+        <v>6762694</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131703046</v>
+        <v>131701230</v>
       </c>
       <c r="B3" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454349</v>
+        <v>454309</v>
       </c>
       <c r="R3" t="n">
-        <v>6762694</v>
+        <v>6762728</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>131699481</v>
       </c>
       <c r="B4" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>131698769</v>
       </c>
       <c r="B5" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>131704892</v>
       </c>
       <c r="B6" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131700972</v>
+        <v>131700622</v>
       </c>
       <c r="B7" t="n">
-        <v>57907</v>
+        <v>79893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,39 +1181,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454349</v>
+        <v>454380</v>
       </c>
       <c r="R7" t="n">
-        <v>6762723</v>
+        <v>6762722</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131700907</v>
+        <v>131700972</v>
       </c>
       <c r="B8" t="n">
-        <v>79269</v>
+        <v>57912</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,37 +1278,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454348</v>
+        <v>454349</v>
       </c>
       <c r="R8" t="n">
-        <v>6762712</v>
+        <v>6762723</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1343,11 +1343,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,10 +1369,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131700622</v>
+        <v>131700907</v>
       </c>
       <c r="B9" t="n">
-        <v>79888</v>
+        <v>79274</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1380,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,13 +1404,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454380</v>
+        <v>454348</v>
       </c>
       <c r="R9" t="n">
-        <v>6762722</v>
+        <v>6762712</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1445,6 +1440,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,53 +1471,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131704688</v>
+        <v>131702441</v>
       </c>
       <c r="B10" t="n">
-        <v>57095</v>
+        <v>79274</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454233</v>
+        <v>454300</v>
       </c>
       <c r="R10" t="n">
-        <v>6762667</v>
+        <v>6762775</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1551,7 +1546,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Under tjädertall</t>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,48 +1573,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131702441</v>
+        <v>131704688</v>
       </c>
       <c r="B11" t="n">
-        <v>79269</v>
+        <v>57100</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454300</v>
+        <v>454233</v>
       </c>
       <c r="R11" t="n">
-        <v>6762775</v>
+        <v>6762667</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
+          <t>Under tjädertall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,7 +1680,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131701172</v>
+        <v>131699170</v>
       </c>
       <c r="B12" t="n">
         <v>8455</v>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454329</v>
+        <v>454431</v>
       </c>
       <c r="R12" t="n">
-        <v>6762746</v>
+        <v>6762675</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1782,45 +1782,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131698785</v>
+        <v>131701172</v>
       </c>
       <c r="B13" t="n">
-        <v>79269</v>
+        <v>8455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454359</v>
+        <v>454329</v>
       </c>
       <c r="R13" t="n">
-        <v>6762685</v>
+        <v>6762746</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1879,50 +1884,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131699170</v>
+        <v>131698785</v>
       </c>
       <c r="B14" t="n">
-        <v>8455</v>
+        <v>79274</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454431</v>
+        <v>454359</v>
       </c>
       <c r="R14" t="n">
-        <v>6762675</v>
+        <v>6762685</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1984,7 +1984,7 @@
         <v>131699324</v>
       </c>
       <c r="B15" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2078,10 +2078,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131699011</v>
+        <v>131701058</v>
       </c>
       <c r="B16" t="n">
-        <v>57904</v>
+        <v>79864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2089,39 +2089,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454431</v>
+        <v>454329</v>
       </c>
       <c r="R16" t="n">
-        <v>6762675</v>
+        <v>6762746</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2180,10 +2175,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131701058</v>
+        <v>131699011</v>
       </c>
       <c r="B17" t="n">
-        <v>79859</v>
+        <v>57909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,34 +2186,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454329</v>
+        <v>454431</v>
       </c>
       <c r="R17" t="n">
-        <v>6762746</v>
+        <v>6762675</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2280,7 +2280,7 @@
         <v>131700625</v>
       </c>
       <c r="B18" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>131704301</v>
       </c>
       <c r="B20" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>131699864</v>
       </c>
       <c r="B21" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131701072</v>
+        <v>131699226</v>
       </c>
       <c r="B22" t="n">
-        <v>79269</v>
+        <v>57912</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,34 +2686,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454329</v>
+        <v>454445</v>
       </c>
       <c r="R22" t="n">
-        <v>6762746</v>
+        <v>6762675</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2772,10 +2777,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131699226</v>
+        <v>131701072</v>
       </c>
       <c r="B23" t="n">
-        <v>57907</v>
+        <v>79274</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2783,39 +2788,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454445</v>
+        <v>454329</v>
       </c>
       <c r="R23" t="n">
-        <v>6762675</v>
+        <v>6762746</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131704207</v>
+        <v>131701061</v>
       </c>
       <c r="B24" t="n">
-        <v>79269</v>
+        <v>79893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2885,21 +2885,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454293</v>
+        <v>454329</v>
       </c>
       <c r="R24" t="n">
-        <v>6762667</v>
+        <v>6762746</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2971,10 +2971,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131700974</v>
+        <v>131704207</v>
       </c>
       <c r="B25" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,10 +3006,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454349</v>
+        <v>454293</v>
       </c>
       <c r="R25" t="n">
-        <v>6762723</v>
+        <v>6762667</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3068,10 +3068,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131701061</v>
+        <v>131700974</v>
       </c>
       <c r="B26" t="n">
-        <v>79888</v>
+        <v>79274</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3079,21 +3079,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454329</v>
+        <v>454349</v>
       </c>
       <c r="R26" t="n">
-        <v>6762746</v>
+        <v>6762723</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3168,7 +3168,7 @@
         <v>131699230</v>
       </c>
       <c r="B27" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>131700143</v>
       </c>
       <c r="B28" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3364,10 +3364,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131704612</v>
+        <v>131701164</v>
       </c>
       <c r="B29" t="n">
-        <v>79269</v>
+        <v>57909</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3375,34 +3375,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454234</v>
+        <v>454329</v>
       </c>
       <c r="R29" t="n">
-        <v>6762699</v>
+        <v>6762746</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3461,10 +3466,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131701164</v>
+        <v>131704612</v>
       </c>
       <c r="B30" t="n">
-        <v>57904</v>
+        <v>79274</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3472,39 +3477,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454329</v>
+        <v>454234</v>
       </c>
       <c r="R30" t="n">
-        <v>6762746</v>
+        <v>6762699</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3566,7 +3566,7 @@
         <v>131704877</v>
       </c>
       <c r="B31" t="n">
-        <v>79027</v>
+        <v>79032</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3660,45 +3660,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131700614</v>
+        <v>131699709</v>
       </c>
       <c r="B32" t="n">
-        <v>79859</v>
+        <v>8455</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454380</v>
+        <v>454510</v>
       </c>
       <c r="R32" t="n">
-        <v>6762722</v>
+        <v>6762678</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3757,10 +3762,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131700019</v>
+        <v>131704895</v>
       </c>
       <c r="B33" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3792,10 +3797,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454460</v>
+        <v>454246</v>
       </c>
       <c r="R33" t="n">
-        <v>6762684</v>
+        <v>6762660</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3854,10 +3859,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131704895</v>
+        <v>131700019</v>
       </c>
       <c r="B34" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3889,10 +3894,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454246</v>
+        <v>454460</v>
       </c>
       <c r="R34" t="n">
-        <v>6762660</v>
+        <v>6762684</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3954,7 +3959,7 @@
         <v>131704692</v>
       </c>
       <c r="B35" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4048,50 +4053,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131699709</v>
+        <v>131700614</v>
       </c>
       <c r="B36" t="n">
-        <v>8455</v>
+        <v>79864</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454510</v>
+        <v>454380</v>
       </c>
       <c r="R36" t="n">
-        <v>6762678</v>
+        <v>6762722</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4153,7 +4153,7 @@
         <v>131699483</v>
       </c>
       <c r="B37" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>131699721</v>
       </c>
       <c r="B39" t="n">
-        <v>79270</v>
+        <v>79275</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4446,10 +4446,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131703843</v>
+        <v>131699577</v>
       </c>
       <c r="B40" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4481,13 +4481,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>454311</v>
+        <v>454487</v>
       </c>
       <c r="R40" t="n">
-        <v>6762631</v>
+        <v>6762659</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4517,11 +4517,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4548,10 +4543,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131704203</v>
+        <v>131703645</v>
       </c>
       <c r="B41" t="n">
-        <v>57904</v>
+        <v>57912</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4559,16 +4554,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4588,10 +4583,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454293</v>
+        <v>454323</v>
       </c>
       <c r="R41" t="n">
-        <v>6762667</v>
+        <v>6762672</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4650,10 +4645,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131703645</v>
+        <v>131703843</v>
       </c>
       <c r="B42" t="n">
-        <v>57907</v>
+        <v>79274</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4661,42 +4656,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454323</v>
+        <v>454311</v>
       </c>
       <c r="R42" t="n">
-        <v>6762672</v>
+        <v>6762631</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4726,6 +4716,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4752,10 +4747,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131699577</v>
+        <v>131704203</v>
       </c>
       <c r="B43" t="n">
-        <v>79269</v>
+        <v>57909</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4763,34 +4758,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454487</v>
+        <v>454293</v>
       </c>
       <c r="R43" t="n">
-        <v>6762659</v>
+        <v>6762667</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4954,7 +4954,7 @@
         <v>131698930</v>
       </c>
       <c r="B45" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 7951-2026 artfynd.xlsx
+++ b/artfynd/A 7951-2026 artfynd.xlsx
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131700622</v>
+        <v>131700972</v>
       </c>
       <c r="B7" t="n">
-        <v>79893</v>
+        <v>57912</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,34 +1181,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454380</v>
+        <v>454349</v>
       </c>
       <c r="R7" t="n">
-        <v>6762722</v>
+        <v>6762723</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131700972</v>
+        <v>131700622</v>
       </c>
       <c r="B8" t="n">
-        <v>57912</v>
+        <v>79893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,39 +1283,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454349</v>
+        <v>454380</v>
       </c>
       <c r="R8" t="n">
-        <v>6762723</v>
+        <v>6762722</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1782,50 +1782,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131701172</v>
+        <v>131698785</v>
       </c>
       <c r="B13" t="n">
-        <v>8455</v>
+        <v>79274</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454329</v>
+        <v>454359</v>
       </c>
       <c r="R13" t="n">
-        <v>6762746</v>
+        <v>6762685</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1884,45 +1879,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131698785</v>
+        <v>131701172</v>
       </c>
       <c r="B14" t="n">
-        <v>79274</v>
+        <v>8455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454359</v>
+        <v>454329</v>
       </c>
       <c r="R14" t="n">
-        <v>6762685</v>
+        <v>6762746</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -3165,7 +3165,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131699230</v>
+        <v>131700143</v>
       </c>
       <c r="B27" t="n">
         <v>79274</v>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454445</v>
+        <v>454452</v>
       </c>
       <c r="R27" t="n">
-        <v>6762675</v>
+        <v>6762716</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3236,6 +3236,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt med garnlav i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3262,7 +3267,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131700143</v>
+        <v>131699230</v>
       </c>
       <c r="B28" t="n">
         <v>79274</v>
@@ -3297,13 +3302,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454452</v>
+        <v>454445</v>
       </c>
       <c r="R28" t="n">
-        <v>6762716</v>
+        <v>6762675</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3333,11 +3338,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt med garnlav i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 7951-2026 artfynd.xlsx
+++ b/artfynd/A 7951-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131703046</v>
       </c>
       <c r="B2" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131701230</v>
       </c>
       <c r="B3" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131699481</v>
+        <v>131704892</v>
       </c>
       <c r="B4" t="n">
-        <v>57912</v>
+        <v>79895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,39 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454462</v>
+        <v>454246</v>
       </c>
       <c r="R4" t="n">
-        <v>6762674</v>
+        <v>6762660</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131698769</v>
+        <v>131699481</v>
       </c>
       <c r="B5" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,7 +997,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454359</v>
+        <v>454462</v>
       </c>
       <c r="R5" t="n">
-        <v>6762685</v>
+        <v>6762674</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131704892</v>
+        <v>131698769</v>
       </c>
       <c r="B6" t="n">
-        <v>79893</v>
+        <v>57914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,34 +1079,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454246</v>
+        <v>454359</v>
       </c>
       <c r="R6" t="n">
-        <v>6762660</v>
+        <v>6762685</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131700972</v>
+        <v>131700622</v>
       </c>
       <c r="B7" t="n">
-        <v>57912</v>
+        <v>79895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,39 +1181,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454349</v>
+        <v>454380</v>
       </c>
       <c r="R7" t="n">
-        <v>6762723</v>
+        <v>6762722</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131700622</v>
+        <v>131700972</v>
       </c>
       <c r="B8" t="n">
-        <v>79893</v>
+        <v>57914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,34 +1278,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454380</v>
+        <v>454349</v>
       </c>
       <c r="R8" t="n">
-        <v>6762722</v>
+        <v>6762723</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,7 +1372,7 @@
         <v>131700907</v>
       </c>
       <c r="B9" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>131702441</v>
       </c>
       <c r="B10" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>131704688</v>
       </c>
       <c r="B11" t="n">
-        <v>57100</v>
+        <v>57102</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>131698785</v>
       </c>
       <c r="B13" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>131699324</v>
       </c>
       <c r="B15" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2078,10 +2078,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131701058</v>
+        <v>131699011</v>
       </c>
       <c r="B16" t="n">
-        <v>79864</v>
+        <v>57911</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2089,34 +2089,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454329</v>
+        <v>454431</v>
       </c>
       <c r="R16" t="n">
-        <v>6762746</v>
+        <v>6762675</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2175,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131699011</v>
+        <v>131701058</v>
       </c>
       <c r="B17" t="n">
-        <v>57909</v>
+        <v>79866</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2186,39 +2191,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454431</v>
+        <v>454329</v>
       </c>
       <c r="R17" t="n">
-        <v>6762675</v>
+        <v>6762746</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2280,7 +2280,7 @@
         <v>131700625</v>
       </c>
       <c r="B18" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2476,10 +2476,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131704301</v>
+        <v>131699864</v>
       </c>
       <c r="B20" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454291</v>
+        <v>454488</v>
       </c>
       <c r="R20" t="n">
-        <v>6762688</v>
+        <v>6762699</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,6 +2547,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Miljöbilder och garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2573,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131699864</v>
+        <v>131704301</v>
       </c>
       <c r="B21" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2608,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454488</v>
+        <v>454291</v>
       </c>
       <c r="R21" t="n">
-        <v>6762699</v>
+        <v>6762688</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2644,11 +2649,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Miljöbilder och garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131699226</v>
+        <v>131701072</v>
       </c>
       <c r="B22" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,39 +2686,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454445</v>
+        <v>454329</v>
       </c>
       <c r="R22" t="n">
-        <v>6762675</v>
+        <v>6762746</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2777,10 +2772,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131701072</v>
+        <v>131699226</v>
       </c>
       <c r="B23" t="n">
-        <v>79274</v>
+        <v>57914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2788,34 +2783,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454329</v>
+        <v>454445</v>
       </c>
       <c r="R23" t="n">
-        <v>6762746</v>
+        <v>6762675</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2877,7 +2877,7 @@
         <v>131701061</v>
       </c>
       <c r="B24" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>131704207</v>
       </c>
       <c r="B25" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>131700974</v>
       </c>
       <c r="B26" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>131700143</v>
       </c>
       <c r="B27" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>131699230</v>
       </c>
       <c r="B28" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>131701164</v>
       </c>
       <c r="B29" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131704612</v>
+        <v>131704877</v>
       </c>
       <c r="B30" t="n">
-        <v>79274</v>
+        <v>79034</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3477,21 +3477,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454234</v>
+        <v>454246</v>
       </c>
       <c r="R30" t="n">
-        <v>6762699</v>
+        <v>6762660</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3563,10 +3563,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131704877</v>
+        <v>131704612</v>
       </c>
       <c r="B31" t="n">
-        <v>79032</v>
+        <v>79276</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3574,21 +3574,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454246</v>
+        <v>454234</v>
       </c>
       <c r="R31" t="n">
-        <v>6762660</v>
+        <v>6762699</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3765,7 +3765,7 @@
         <v>131704895</v>
       </c>
       <c r="B33" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>131700019</v>
       </c>
       <c r="B34" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>131704692</v>
       </c>
       <c r="B35" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>131700614</v>
       </c>
       <c r="B36" t="n">
-        <v>79864</v>
+        <v>79866</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>131699483</v>
       </c>
       <c r="B37" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4247,50 +4247,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131699571</v>
+        <v>131699721</v>
       </c>
       <c r="B38" t="n">
-        <v>8455</v>
+        <v>79277</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>230405</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454487</v>
+        <v>454510</v>
       </c>
       <c r="R38" t="n">
-        <v>6762659</v>
+        <v>6762678</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4349,45 +4344,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131699721</v>
+        <v>131699571</v>
       </c>
       <c r="B39" t="n">
-        <v>79275</v>
+        <v>8455</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>230405</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454510</v>
+        <v>454487</v>
       </c>
       <c r="R39" t="n">
-        <v>6762678</v>
+        <v>6762659</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4449,7 +4449,7 @@
         <v>131699577</v>
       </c>
       <c r="B40" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4543,10 +4543,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131703645</v>
+        <v>131703843</v>
       </c>
       <c r="B41" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4554,42 +4554,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454323</v>
+        <v>454311</v>
       </c>
       <c r="R41" t="n">
-        <v>6762672</v>
+        <v>6762631</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4619,6 +4614,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4645,10 +4645,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131703843</v>
+        <v>131704203</v>
       </c>
       <c r="B42" t="n">
-        <v>79274</v>
+        <v>57911</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4656,37 +4656,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>454311</v>
+        <v>454293</v>
       </c>
       <c r="R42" t="n">
-        <v>6762631</v>
+        <v>6762667</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4716,11 +4721,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4747,10 +4747,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131704203</v>
+        <v>131703645</v>
       </c>
       <c r="B43" t="n">
-        <v>57909</v>
+        <v>57914</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4758,16 +4758,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4787,10 +4787,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454293</v>
+        <v>454323</v>
       </c>
       <c r="R43" t="n">
-        <v>6762667</v>
+        <v>6762672</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4954,7 +4954,7 @@
         <v>131698930</v>
       </c>
       <c r="B45" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 7951-2026 artfynd.xlsx
+++ b/artfynd/A 7951-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131703046</v>
       </c>
       <c r="B2" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131701230</v>
       </c>
       <c r="B3" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131698769</v>
+        <v>131699481</v>
       </c>
       <c r="B4" t="n">
         <v>57948</v>
@@ -900,7 +900,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454359</v>
+        <v>454462</v>
       </c>
       <c r="R4" t="n">
-        <v>6762685</v>
+        <v>6762674</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131704892</v>
+        <v>131698769</v>
       </c>
       <c r="B5" t="n">
-        <v>79934</v>
+        <v>57948</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,34 +982,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454246</v>
+        <v>454359</v>
       </c>
       <c r="R5" t="n">
-        <v>6762660</v>
+        <v>6762685</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131699481</v>
+        <v>131704892</v>
       </c>
       <c r="B6" t="n">
-        <v>57948</v>
+        <v>79936</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,39 +1084,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454462</v>
+        <v>454246</v>
       </c>
       <c r="R6" t="n">
-        <v>6762674</v>
+        <v>6762660</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131700622</v>
+        <v>131700972</v>
       </c>
       <c r="B7" t="n">
-        <v>79934</v>
+        <v>57948</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,34 +1181,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454380</v>
+        <v>454349</v>
       </c>
       <c r="R7" t="n">
-        <v>6762722</v>
+        <v>6762723</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131700972</v>
+        <v>131700907</v>
       </c>
       <c r="B8" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,42 +1283,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454349</v>
+        <v>454348</v>
       </c>
       <c r="R8" t="n">
-        <v>6762723</v>
+        <v>6762712</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1343,6 +1343,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1369,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131700907</v>
+        <v>131700622</v>
       </c>
       <c r="B9" t="n">
-        <v>79315</v>
+        <v>79936</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1380,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1404,13 +1409,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454348</v>
+        <v>454380</v>
       </c>
       <c r="R9" t="n">
-        <v>6762712</v>
+        <v>6762722</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1440,11 +1445,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,53 +1471,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131704688</v>
+        <v>131702441</v>
       </c>
       <c r="B10" t="n">
-        <v>57136</v>
+        <v>79317</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454233</v>
+        <v>454300</v>
       </c>
       <c r="R10" t="n">
-        <v>6762667</v>
+        <v>6762775</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1551,7 +1546,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Under tjädertall</t>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,48 +1573,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131702441</v>
+        <v>131704688</v>
       </c>
       <c r="B11" t="n">
-        <v>79315</v>
+        <v>57136</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454300</v>
+        <v>454233</v>
       </c>
       <c r="R11" t="n">
-        <v>6762775</v>
+        <v>6762667</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
+          <t>Under tjädertall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,50 +1680,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131699170</v>
+        <v>131698785</v>
       </c>
       <c r="B12" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454431</v>
+        <v>454359</v>
       </c>
       <c r="R12" t="n">
-        <v>6762675</v>
+        <v>6762685</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1782,45 +1777,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131698785</v>
+        <v>131699170</v>
       </c>
       <c r="B13" t="n">
-        <v>79315</v>
+        <v>8455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454359</v>
+        <v>454431</v>
       </c>
       <c r="R13" t="n">
-        <v>6762685</v>
+        <v>6762675</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1984,7 +1984,7 @@
         <v>131699324</v>
       </c>
       <c r="B15" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2078,10 +2078,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131701058</v>
+        <v>131699011</v>
       </c>
       <c r="B16" t="n">
-        <v>79905</v>
+        <v>57945</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2089,34 +2089,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454329</v>
+        <v>454431</v>
       </c>
       <c r="R16" t="n">
-        <v>6762746</v>
+        <v>6762675</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2175,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131699011</v>
+        <v>131701058</v>
       </c>
       <c r="B17" t="n">
-        <v>57945</v>
+        <v>79907</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2186,39 +2191,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454431</v>
+        <v>454329</v>
       </c>
       <c r="R17" t="n">
-        <v>6762675</v>
+        <v>6762746</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2277,50 +2277,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131700699</v>
+        <v>131700625</v>
       </c>
       <c r="B18" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454367</v>
+        <v>454380</v>
       </c>
       <c r="R18" t="n">
-        <v>6762713</v>
+        <v>6762722</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2379,45 +2374,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131700625</v>
+        <v>131700699</v>
       </c>
       <c r="B19" t="n">
-        <v>79315</v>
+        <v>8455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454380</v>
+        <v>454367</v>
       </c>
       <c r="R19" t="n">
-        <v>6762722</v>
+        <v>6762713</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2476,10 +2476,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131704301</v>
+        <v>131699864</v>
       </c>
       <c r="B20" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454291</v>
+        <v>454488</v>
       </c>
       <c r="R20" t="n">
-        <v>6762688</v>
+        <v>6762699</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,6 +2547,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Miljöbilder och garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2573,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131699864</v>
+        <v>131704301</v>
       </c>
       <c r="B21" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2608,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454488</v>
+        <v>454291</v>
       </c>
       <c r="R21" t="n">
-        <v>6762699</v>
+        <v>6762688</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2644,11 +2649,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Miljöbilder och garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131701072</v>
+        <v>131699226</v>
       </c>
       <c r="B22" t="n">
-        <v>79315</v>
+        <v>57948</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,34 +2686,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454329</v>
+        <v>454445</v>
       </c>
       <c r="R22" t="n">
-        <v>6762746</v>
+        <v>6762675</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2772,10 +2777,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131699226</v>
+        <v>131701072</v>
       </c>
       <c r="B23" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2783,39 +2788,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454445</v>
+        <v>454329</v>
       </c>
       <c r="R23" t="n">
-        <v>6762675</v>
+        <v>6762746</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2877,7 +2877,7 @@
         <v>131704207</v>
       </c>
       <c r="B24" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>131700974</v>
       </c>
       <c r="B25" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>131701061</v>
       </c>
       <c r="B26" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3165,10 +3165,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131700143</v>
+        <v>131699230</v>
       </c>
       <c r="B27" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454452</v>
+        <v>454445</v>
       </c>
       <c r="R27" t="n">
-        <v>6762716</v>
+        <v>6762675</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3236,11 +3236,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt med garnlav i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3267,10 +3262,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131699230</v>
+        <v>131700143</v>
       </c>
       <c r="B28" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3302,13 +3297,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454445</v>
+        <v>454452</v>
       </c>
       <c r="R28" t="n">
-        <v>6762675</v>
+        <v>6762716</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3338,6 +3333,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt med garnlav i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3367,7 +3367,7 @@
         <v>131704612</v>
       </c>
       <c r="B29" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>131704877</v>
       </c>
       <c r="B31" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3660,50 +3660,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131699709</v>
+        <v>131700614</v>
       </c>
       <c r="B32" t="n">
-        <v>8455</v>
+        <v>79907</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454510</v>
+        <v>454380</v>
       </c>
       <c r="R32" t="n">
-        <v>6762678</v>
+        <v>6762722</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3765,7 +3760,7 @@
         <v>131704895</v>
       </c>
       <c r="B33" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3859,10 +3854,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131704692</v>
+        <v>131700019</v>
       </c>
       <c r="B34" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3894,10 +3889,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454233</v>
+        <v>454460</v>
       </c>
       <c r="R34" t="n">
-        <v>6762667</v>
+        <v>6762684</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3956,10 +3951,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131700019</v>
+        <v>131704692</v>
       </c>
       <c r="B35" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3991,10 +3986,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454460</v>
+        <v>454233</v>
       </c>
       <c r="R35" t="n">
-        <v>6762684</v>
+        <v>6762667</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4053,45 +4048,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131700614</v>
+        <v>131699709</v>
       </c>
       <c r="B36" t="n">
-        <v>79905</v>
+        <v>8455</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>454380</v>
+        <v>454510</v>
       </c>
       <c r="R36" t="n">
-        <v>6762722</v>
+        <v>6762678</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4153,7 +4153,7 @@
         <v>131699483</v>
       </c>
       <c r="B37" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4247,45 +4247,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131699721</v>
+        <v>131699571</v>
       </c>
       <c r="B38" t="n">
-        <v>79316</v>
+        <v>8455</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>230405</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>454510</v>
+        <v>454487</v>
       </c>
       <c r="R38" t="n">
-        <v>6762678</v>
+        <v>6762659</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4344,50 +4349,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131699571</v>
+        <v>131699721</v>
       </c>
       <c r="B39" t="n">
-        <v>8455</v>
+        <v>79318</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>230405</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>454487</v>
+        <v>454510</v>
       </c>
       <c r="R39" t="n">
-        <v>6762659</v>
+        <v>6762678</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4449,7 +4449,7 @@
         <v>131699577</v>
       </c>
       <c r="B40" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4543,10 +4543,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131703843</v>
+        <v>131704203</v>
       </c>
       <c r="B41" t="n">
-        <v>79315</v>
+        <v>57945</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4554,37 +4554,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>454311</v>
+        <v>454293</v>
       </c>
       <c r="R41" t="n">
-        <v>6762631</v>
+        <v>6762667</v>
       </c>
       <c r="S41" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4614,11 +4619,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4747,10 +4747,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131704203</v>
+        <v>131703843</v>
       </c>
       <c r="B43" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4758,42 +4758,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>454293</v>
+        <v>454311</v>
       </c>
       <c r="R43" t="n">
-        <v>6762667</v>
+        <v>6762631</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4823,6 +4818,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt till måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4954,7 +4954,7 @@
         <v>131698930</v>
       </c>
       <c r="B45" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 7951-2026 artfynd.xlsx
+++ b/artfynd/A 7951-2026 artfynd.xlsx
@@ -1680,45 +1680,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131698785</v>
+        <v>131699170</v>
       </c>
       <c r="B12" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454359</v>
+        <v>454431</v>
       </c>
       <c r="R12" t="n">
-        <v>6762685</v>
+        <v>6762675</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,50 +1782,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131699170</v>
+        <v>131698785</v>
       </c>
       <c r="B13" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454431</v>
+        <v>454359</v>
       </c>
       <c r="R13" t="n">
-        <v>6762675</v>
+        <v>6762685</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131699226</v>
+        <v>131701072</v>
       </c>
       <c r="B22" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,39 +2686,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454445</v>
+        <v>454329</v>
       </c>
       <c r="R22" t="n">
-        <v>6762675</v>
+        <v>6762746</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2777,10 +2772,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131701072</v>
+        <v>131699226</v>
       </c>
       <c r="B23" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2788,34 +2783,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kuppnäset, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454329</v>
+        <v>454445</v>
       </c>
       <c r="R23" t="n">
-        <v>6762746</v>
+        <v>6762675</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3364,10 +3364,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131704612</v>
+        <v>131704877</v>
       </c>
       <c r="B29" t="n">
-        <v>79317</v>
+        <v>79075</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3375,21 +3375,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454234</v>
+        <v>454246</v>
       </c>
       <c r="R29" t="n">
-        <v>6762699</v>
+        <v>6762660</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3563,10 +3563,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131704877</v>
+        <v>131704612</v>
       </c>
       <c r="B31" t="n">
-        <v>79075</v>
+        <v>79317</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3574,21 +3574,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454246</v>
+        <v>454234</v>
       </c>
       <c r="R31" t="n">
-        <v>6762660</v>
+        <v>6762699</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3660,10 +3660,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131700614</v>
+        <v>131704895</v>
       </c>
       <c r="B32" t="n">
-        <v>79907</v>
+        <v>79317</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3671,21 +3671,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>454380</v>
+        <v>454246</v>
       </c>
       <c r="R32" t="n">
-        <v>6762722</v>
+        <v>6762660</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3757,7 +3757,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131704895</v>
+        <v>131700019</v>
       </c>
       <c r="B33" t="n">
         <v>79317</v>
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>454246</v>
+        <v>454460</v>
       </c>
       <c r="R33" t="n">
-        <v>6762660</v>
+        <v>6762684</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131700019</v>
+        <v>131704692</v>
       </c>
       <c r="B34" t="n">
         <v>79317</v>
@@ -3889,10 +3889,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>454460</v>
+        <v>454233</v>
       </c>
       <c r="R34" t="n">
-        <v>6762684</v>
+        <v>6762667</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3951,10 +3951,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131704692</v>
+        <v>131700614</v>
       </c>
       <c r="B35" t="n">
-        <v>79317</v>
+        <v>79907</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3962,21 +3962,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3986,10 +3986,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>454233</v>
+        <v>454380</v>
       </c>
       <c r="R35" t="n">
-        <v>6762667</v>
+        <v>6762722</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
